--- a/BeatnotePostCombFix/TemperaturesByDate.xlsx
+++ b/BeatnotePostCombFix/TemperaturesByDate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostCombFix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{577F71F4-4124-4C40-878F-B61DDE43218C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DEFF52-620C-463A-A1A3-E523FD545027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0F3876EE-4319-423F-999C-843E10C0156F}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -46,16 +46,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -63,15 +75,112 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="16" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="1" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="1" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -384,94 +493,111 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6AC70B1-FE45-4E6D-BAE1-1DE1DFC69942}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="8">
+        <v>46114</v>
+      </c>
+      <c r="B1" s="9">
+        <v>18.595500000000001</v>
+      </c>
+      <c r="C1" s="10">
+        <v>41.803179999999998</v>
+      </c>
+      <c r="G1" s="1">
+        <v>46107</v>
+      </c>
+      <c r="H1">
+        <v>5.4348999999999998</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="11">
         <v>46113</v>
       </c>
-      <c r="B1">
+      <c r="B2" s="12">
         <v>18.603090000000002</v>
       </c>
-      <c r="C1">
+      <c r="C2" s="13">
         <v>42.096380000000003</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="11">
         <v>46107</v>
       </c>
-      <c r="B2">
+      <c r="B3" s="12">
         <v>18.592289999999998</v>
       </c>
-      <c r="C2">
+      <c r="C3" s="13">
         <v>41.689749999999997</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="11">
         <v>46105</v>
       </c>
-      <c r="B3">
+      <c r="B4" s="12">
         <v>18.59431</v>
       </c>
-      <c r="C3">
+      <c r="C4" s="13">
         <v>41.99982</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="14">
         <v>46097</v>
       </c>
-      <c r="B4">
+      <c r="B5" s="15">
         <v>18.6008</v>
       </c>
-      <c r="C4">
+      <c r="C5" s="16">
         <v>42.153590000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>46094</v>
       </c>
-      <c r="B5">
+      <c r="B6" s="3">
         <v>16.680520000000001</v>
       </c>
-      <c r="C5">
+      <c r="C6" s="4">
         <v>41.983820000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <v>46092</v>
       </c>
-      <c r="B6">
+      <c r="B7" s="6">
         <v>16.665220000000001</v>
       </c>
-      <c r="C6">
+      <c r="C7" s="7">
         <v>41.862870000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>46090</v>
       </c>
-      <c r="B7">
+      <c r="B8" s="3">
         <v>26.3291</v>
       </c>
-      <c r="C7">
+      <c r="C8" s="4">
         <v>42.454419999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <v>46086</v>
       </c>
-      <c r="B8">
+      <c r="B9" s="6">
         <v>23.771409999999999</v>
       </c>
-      <c r="C8">
+      <c r="C9" s="7">
         <v>42.464019999999998</v>
       </c>
     </row>
